--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -1602,10 +1602,10 @@
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="R7" s="5">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="S7" s="5">
         <v>3000</v>
@@ -1623,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7" s="5">
         <v>0</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23520" windowHeight="11670"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CastProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
   <si>
     <t>selectParam</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>技能开始特效</t>
+  </si>
+  <si>
+    <t>技能命中自己特效</t>
   </si>
   <si>
     <t>技能命中特效</t>
@@ -1335,19 +1338,19 @@
         <v>22</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="3:26">
@@ -1358,144 +1361,144 @@
         <v>6</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="3:26">
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="G5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K5" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="3:26">
@@ -1506,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" s="5">
         <v>2</v>
@@ -1515,24 +1518,24 @@
         <v>2000</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J6" s="5">
         <v>2</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5">
@@ -1551,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="W6" s="5" t="b">
         <v>1</v>
@@ -1574,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="5">
         <v>2</v>
@@ -1583,19 +1586,19 @@
         <v>5000</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J7" s="5">
         <v>2</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
@@ -1617,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W7" s="5" t="b">
         <v>1</v>
@@ -1640,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1697,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -1706,7 +1709,7 @@
         <v>5000</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
@@ -1754,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" s="5">
         <v>3</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="16680" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="CastProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="73">
   <si>
     <t>selectParam</t>
   </si>
@@ -79,6 +79,9 @@
     <t>命中自身行为</t>
   </si>
   <si>
+    <t>结束行为</t>
+  </si>
+  <si>
     <t>技能命中自身时间点</t>
   </si>
   <si>
@@ -143,6 +146,9 @@
   </si>
   <si>
     <t>SelfHitAction</t>
+  </si>
+  <si>
+    <t>FinishAction</t>
   </si>
   <si>
     <t>SelfHitActionTimes</t>
@@ -1237,7 +1243,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:Z10"/>
+  <dimension ref="C1:AA10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -1247,39 +1253,39 @@
     <col min="7" max="8" width="11" style="1" customWidth="1"/>
     <col min="9" max="9" width="28.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="15.25" style="1" customWidth="1"/>
-    <col min="11" max="14" width="15.25" style="2" customWidth="1"/>
-    <col min="15" max="16" width="15.25" style="1" customWidth="1"/>
-    <col min="17" max="17" width="40.625" style="1" customWidth="1"/>
-    <col min="18" max="26" width="15.25" style="1" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="1"/>
+    <col min="11" max="15" width="15.25" style="2" customWidth="1"/>
+    <col min="16" max="17" width="15.25" style="1" customWidth="1"/>
+    <col min="18" max="18" width="40.625" style="1" customWidth="1"/>
+    <col min="19" max="27" width="15.25" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:26">
+    <row r="1" spans="3:27">
       <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="3:26">
+    <row r="2" spans="3:27">
       <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="X2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="Y2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AA2" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="3:26">
+    <row r="3" spans="3:27">
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1316,7 +1322,7 @@
       <c r="N3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="P3" s="3" t="s">
@@ -1352,8 +1358,11 @@
       <c r="Z3" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA3" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="4" spans="3:26">
+    <row r="4" spans="3:27">
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1361,147 +1370,153 @@
         <v>6</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="O4" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="P4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="5" spans="3:26">
+    <row r="5" spans="3:27">
       <c r="C5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="K5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="Z5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="W5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z5" s="3" t="s">
-        <v>50</v>
+      <c r="AA5" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="6" spans="3:26">
+    <row r="6" spans="3:27">
       <c r="C6" s="5">
         <v>66001</v>
       </c>
@@ -1509,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F6" s="5">
         <v>2</v>
@@ -1518,58 +1533,59 @@
         <v>2000</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J6" s="5">
         <v>2</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5">
-        <v>400</v>
-      </c>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q6" s="5"/>
       <c r="R6" s="5">
         <v>400</v>
       </c>
       <c r="S6" s="5">
+        <v>400</v>
+      </c>
+      <c r="T6" s="5">
         <v>3000</v>
       </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
       <c r="U6" s="5">
         <v>0</v>
       </c>
-      <c r="V6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="W6" s="5" t="b">
+      <c r="V6" s="5">
+        <v>0</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="X6" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="X6" s="5">
+      <c r="Y6" s="5">
         <v>6</v>
       </c>
-      <c r="Y6" s="5">
-        <v>0</v>
-      </c>
       <c r="Z6" s="5">
         <v>0</v>
       </c>
+      <c r="AA6" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="3:26">
+    <row r="7" spans="3:27">
       <c r="C7" s="5">
         <v>66002</v>
       </c>
@@ -1577,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F7" s="5">
         <v>2</v>
@@ -1586,56 +1602,57 @@
         <v>5000</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J7" s="5">
         <v>2</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="5"/>
+      <c r="O7" s="6"/>
       <c r="P7" s="5"/>
-      <c r="Q7" s="5">
-        <v>800</v>
-      </c>
+      <c r="Q7" s="5"/>
       <c r="R7" s="5">
         <v>800</v>
       </c>
       <c r="S7" s="5">
+        <v>800</v>
+      </c>
+      <c r="T7" s="5">
         <v>3000</v>
       </c>
-      <c r="T7" s="5">
+      <c r="U7" s="5">
         <v>22003</v>
       </c>
-      <c r="U7" s="5">
-        <v>0</v>
-      </c>
-      <c r="V7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="W7" s="5" t="b">
+      <c r="V7" s="5">
+        <v>0</v>
+      </c>
+      <c r="W7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="X7" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="X7" s="5">
+      <c r="Y7" s="5">
         <v>5</v>
       </c>
-      <c r="Y7" s="5">
-        <v>0</v>
-      </c>
       <c r="Z7" s="5">
         <v>0</v>
       </c>
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="3:26">
+    <row r="8" spans="3:27">
       <c r="C8" s="5">
         <v>66003</v>
       </c>
@@ -1643,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1661,11 +1678,9 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="5"/>
+      <c r="O8" s="6"/>
       <c r="P8" s="5"/>
-      <c r="Q8" s="5">
-        <v>0</v>
-      </c>
+      <c r="Q8" s="5"/>
       <c r="R8" s="5">
         <v>0</v>
       </c>
@@ -1681,18 +1696,21 @@
       <c r="V8" s="5">
         <v>0</v>
       </c>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5">
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5">
         <v>6</v>
       </c>
-      <c r="Y8" s="5">
-        <v>0</v>
-      </c>
       <c r="Z8" s="5">
         <v>0</v>
       </c>
+      <c r="AA8" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="3:26">
+    <row r="9" spans="3:27">
       <c r="C9" s="5">
         <v>66004</v>
       </c>
@@ -1700,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -1709,7 +1727,7 @@
         <v>5000</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
@@ -1718,11 +1736,9 @@
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="5"/>
+      <c r="O9" s="6"/>
       <c r="P9" s="5"/>
-      <c r="Q9" s="5">
-        <v>0</v>
-      </c>
+      <c r="Q9" s="5"/>
       <c r="R9" s="5">
         <v>0</v>
       </c>
@@ -1738,18 +1754,21 @@
       <c r="V9" s="5">
         <v>0</v>
       </c>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5">
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5">
         <v>6</v>
       </c>
-      <c r="Y9" s="5">
-        <v>0</v>
-      </c>
       <c r="Z9" s="5">
         <v>0</v>
       </c>
+      <c r="AA9" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="3:26">
+    <row r="10" spans="3:27">
       <c r="C10" s="5">
         <v>66005</v>
       </c>
@@ -1757,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F10" s="5">
         <v>3</v>
@@ -1775,11 +1794,9 @@
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
-      <c r="O10" s="5"/>
+      <c r="O10" s="6"/>
       <c r="P10" s="5"/>
-      <c r="Q10" s="5">
-        <v>0</v>
-      </c>
+      <c r="Q10" s="5"/>
       <c r="R10" s="5">
         <v>0</v>
       </c>
@@ -1795,14 +1812,17 @@
       <c r="V10" s="5">
         <v>0</v>
       </c>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5">
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5">
         <v>6</v>
       </c>
-      <c r="Y10" s="5">
-        <v>0</v>
-      </c>
       <c r="Z10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="5">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16680" windowHeight="11775"/>
+    <workbookView windowWidth="23760" windowHeight="7365"/>
   </bookViews>
   <sheets>
     <sheet name="CastProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
   <si>
     <t>selectParam</t>
   </si>
@@ -244,13 +244,16 @@
     <t>技能名字3</t>
   </si>
   <si>
-    <t>技能名字4</t>
-  </si>
-  <si>
-    <t>1,3000,3,1</t>
-  </si>
-  <si>
-    <t>技能名字5</t>
+    <t>1,500,1,1</t>
+  </si>
+  <si>
+    <t>选中一个坐标释放真子弹</t>
+  </si>
+  <si>
+    <t>77006</t>
+  </si>
+  <si>
+    <t>150</t>
   </si>
 </sst>
 </file>
@@ -1243,8 +1246,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AA10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="C1:AA8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -1663,32 +1666,37 @@
         <v>69</v>
       </c>
       <c r="F8" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="5">
-        <v>5000</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0</v>
+        <v>3000</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
+      <c r="O8" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="S8" s="5">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="T8" s="5">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U8" s="5">
         <v>0</v>
@@ -1699,130 +1707,16 @@
       <c r="W8" s="5">
         <v>0</v>
       </c>
-      <c r="X8" s="5"/>
+      <c r="X8" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="Y8" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8" s="5">
         <v>0</v>
       </c>
       <c r="AA8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:27">
-      <c r="C9" s="5">
-        <v>66004</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="5">
-        <v>2</v>
-      </c>
-      <c r="G9" s="5">
-        <v>5000</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
-        <v>0</v>
-      </c>
-      <c r="T9" s="5">
-        <v>0</v>
-      </c>
-      <c r="U9" s="5">
-        <v>0</v>
-      </c>
-      <c r="V9" s="5">
-        <v>0</v>
-      </c>
-      <c r="W9" s="5">
-        <v>0</v>
-      </c>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5">
-        <v>6</v>
-      </c>
-      <c r="Z9" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:27">
-      <c r="C10" s="5">
-        <v>66005</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="5">
-        <v>3</v>
-      </c>
-      <c r="G10" s="5">
-        <v>5000</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5">
-        <v>0</v>
-      </c>
-      <c r="W10" s="5">
-        <v>0</v>
-      </c>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5">
-        <v>6</v>
-      </c>
-      <c r="Z10" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="5">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23760" windowHeight="7365"/>
+    <workbookView windowWidth="24720" windowHeight="9705"/>
   </bookViews>
   <sheets>
     <sheet name="CastProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="80">
   <si>
     <t>selectParam</t>
   </si>
@@ -254,6 +254,24 @@
   </si>
   <si>
     <t>150</t>
+  </si>
+  <si>
+    <t>技能名字4</t>
+  </si>
+  <si>
+    <t>选中一个目标测试真子弹</t>
+  </si>
+  <si>
+    <t>77009</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>真子弹照成伤害</t>
+  </si>
+  <si>
+    <t>77010</t>
   </si>
 </sst>
 </file>
@@ -1246,8 +1264,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AA8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="C1:AA10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -1690,10 +1708,10 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="S8" s="5">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="T8" s="5">
         <v>5000</v>
@@ -1717,6 +1735,133 @@
         <v>0</v>
       </c>
       <c r="AA8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:27">
+      <c r="C9" s="5">
+        <v>66004</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5">
+        <v>500</v>
+      </c>
+      <c r="S9" s="5">
+        <v>500</v>
+      </c>
+      <c r="T9" s="5">
+        <v>5000</v>
+      </c>
+      <c r="U9" s="5">
+        <v>22003</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0</v>
+      </c>
+      <c r="W9" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="X9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:27">
+      <c r="C10" s="5">
+        <v>66005</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="5">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5">
+        <v>-1</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5"/>
+      <c r="W10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="X10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="5">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="81">
   <si>
     <t>selectParam</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>77010</t>
+  </si>
+  <si>
+    <t>77012</t>
   </si>
 </sst>
 </file>
@@ -1264,7 +1267,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AA10"/>
+  <dimension ref="C1:AA11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -1865,6 +1868,73 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="3:27">
+      <c r="C11" s="5">
+        <v>66006</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5">
+        <v>500</v>
+      </c>
+      <c r="S11" s="5">
+        <v>500</v>
+      </c>
+      <c r="T11" s="5">
+        <v>5000</v>
+      </c>
+      <c r="U11" s="5">
+        <v>22003</v>
+      </c>
+      <c r="V11" s="5">
+        <v>0</v>
+      </c>
+      <c r="W11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="X11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>5</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
   <si>
     <t>selectParam</t>
   </si>
@@ -202,6 +202,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>#普攻</t>
+  </si>
+  <si>
     <t>技能名字1</t>
   </si>
   <si>
@@ -223,6 +226,9 @@
     <t>22001,22001</t>
   </si>
   <si>
+    <t>#假子弹</t>
+  </si>
+  <si>
     <t>技能名字2</t>
   </si>
   <si>
@@ -256,6 +262,9 @@
     <t>150</t>
   </si>
   <si>
+    <t>#陨石</t>
+  </si>
+  <si>
     <t>技能名字4</t>
   </si>
   <si>
@@ -274,7 +283,16 @@
     <t>77010</t>
   </si>
   <si>
+    <t>#虚空发球</t>
+  </si>
+  <si>
     <t>77012</t>
+  </si>
+  <si>
+    <t>虚空发球吸引</t>
+  </si>
+  <si>
+    <t>77013</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AA11"/>
+  <dimension ref="B1:AA16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -1284,7 +1302,7 @@
     <col min="28" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:27">
+    <row r="1" spans="2:27">
       <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1295,7 +1313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="3:27">
+    <row r="2" spans="2:27">
       <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1309,7 +1327,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="3:27">
+    <row r="3" spans="2:27">
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1386,7 +1404,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="3:27">
+    <row r="4" spans="2:27">
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1463,7 +1481,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="3:27">
+    <row r="5" spans="2:27">
       <c r="C5" s="3" t="s">
         <v>52</v>
       </c>
@@ -1540,134 +1558,97 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="3:27">
-      <c r="C6" s="5">
-        <v>66001</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5" t="s">
+    <row r="6" spans="2:27">
+      <c r="B6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="5">
-        <v>2</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" s="5">
-        <v>2</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
-      <c r="P6" s="6" t="s">
-        <v>61</v>
-      </c>
+      <c r="P6" s="6"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="5">
-        <v>400</v>
-      </c>
-      <c r="S6" s="5">
-        <v>400</v>
-      </c>
-      <c r="T6" s="5">
-        <v>3000</v>
-      </c>
-      <c r="U6" s="5">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5">
-        <v>0</v>
-      </c>
-      <c r="W6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="X6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="5">
-        <v>6</v>
-      </c>
-      <c r="Z6" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="5">
-        <v>0</v>
-      </c>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
     </row>
-    <row r="7" spans="3:27">
+    <row r="7" spans="2:27">
       <c r="C7" s="5">
-        <v>66002</v>
+        <v>66001</v>
       </c>
       <c r="D7" s="5">
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F7" s="5">
         <v>2</v>
       </c>
       <c r="G7" s="5">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J7" s="5">
         <v>2</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
-      <c r="P7" s="5"/>
+      <c r="P7" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="S7" s="5">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="T7" s="5">
         <v>3000</v>
       </c>
       <c r="U7" s="5">
-        <v>22003</v>
+        <v>0</v>
       </c>
       <c r="V7" s="5">
         <v>0</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="X7" s="5" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7" s="5">
         <v>0</v>
@@ -1676,80 +1657,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:27">
-      <c r="C8" s="5">
-        <v>66003</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" s="5">
-        <v>3</v>
-      </c>
-      <c r="G8" s="5">
-        <v>3000</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" s="5">
-        <v>2</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>72</v>
-      </c>
+    <row r="8" spans="2:27">
+      <c r="B8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="P8" s="5"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
       <c r="Q8" s="5"/>
-      <c r="R8" s="5">
-        <v>500</v>
-      </c>
-      <c r="S8" s="5">
-        <v>500</v>
-      </c>
-      <c r="T8" s="5">
-        <v>5000</v>
-      </c>
-      <c r="U8" s="5">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5">
-        <v>0</v>
-      </c>
-      <c r="W8" s="5">
-        <v>0</v>
-      </c>
-      <c r="X8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="5">
-        <v>5</v>
-      </c>
-      <c r="Z8" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="5">
-        <v>0</v>
-      </c>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
     </row>
-    <row r="9" spans="3:27">
+    <row r="9" spans="2:27">
       <c r="C9" s="5">
-        <v>66004</v>
+        <v>66002</v>
       </c>
       <c r="D9" s="5">
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -1758,33 +1703,33 @@
         <v>5000</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="J9" s="5">
         <v>2</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6" t="s">
-        <v>76</v>
-      </c>
+      <c r="K9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="6" t="s">
-        <v>73</v>
-      </c>
+      <c r="O9" s="6"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="S9" s="5">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="T9" s="5">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="U9" s="5">
         <v>22003</v>
@@ -1793,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="X9" s="5" t="b">
         <v>1</v>
@@ -1808,58 +1753,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:27">
+    <row r="10" spans="2:27">
       <c r="C10" s="5">
-        <v>66005</v>
+        <v>66003</v>
       </c>
       <c r="D10" s="5">
         <v>1</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="5">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="5">
-        <v>4</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M10" s="6"/>
-      <c r="O10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5">
-        <v>-1</v>
+        <v>500</v>
       </c>
       <c r="S10" s="5">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="T10" s="5">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U10" s="5">
         <v>0</v>
       </c>
-      <c r="V10" s="5"/>
-      <c r="W10" s="6" t="s">
-        <v>77</v>
+      <c r="V10" s="5">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5">
+        <v>0</v>
       </c>
       <c r="X10" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z10" s="5">
         <v>0</v>
@@ -1868,70 +1818,312 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:27">
-      <c r="C11" s="5">
-        <v>66006</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="5">
-        <v>2</v>
-      </c>
-      <c r="G11" s="5">
-        <v>5000</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="5">
-        <v>2</v>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6" t="s">
-        <v>80</v>
-      </c>
+    <row r="11" spans="2:27">
+      <c r="B11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="M11" s="6"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="6" t="s">
-        <v>73</v>
-      </c>
+      <c r="O11" s="6"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
-      <c r="R11" s="5">
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+    </row>
+    <row r="12" spans="2:27">
+      <c r="C12" s="5">
+        <v>66004</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="5">
+        <v>2</v>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5">
         <v>500</v>
       </c>
-      <c r="S11" s="5">
+      <c r="S12" s="5">
         <v>500</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T12" s="5">
         <v>5000</v>
       </c>
-      <c r="U11" s="5">
+      <c r="U12" s="5">
         <v>22003</v>
       </c>
-      <c r="V11" s="5">
-        <v>0</v>
-      </c>
-      <c r="W11" s="6" t="s">
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="X12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:27">
+      <c r="C13" s="5">
+        <v>66005</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="X11" s="5" t="b">
+      <c r="F13" s="5">
+        <v>4</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5">
+        <v>-1</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5"/>
+      <c r="W13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="X13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:27">
+      <c r="B14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+    </row>
+    <row r="15" spans="2:27">
+      <c r="C15" s="5">
+        <v>66006</v>
+      </c>
+      <c r="D15" s="5">
         <v>1</v>
       </c>
-      <c r="Y11" s="5">
+      <c r="E15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" s="5">
+        <v>2</v>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5">
+        <v>500</v>
+      </c>
+      <c r="S15" s="5">
+        <v>500</v>
+      </c>
+      <c r="T15" s="5">
+        <v>5000</v>
+      </c>
+      <c r="U15" s="5">
+        <v>22003</v>
+      </c>
+      <c r="V15" s="5">
+        <v>0</v>
+      </c>
+      <c r="W15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="X15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="5">
         <v>5</v>
       </c>
-      <c r="Z11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="5">
+      <c r="Z15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27">
+      <c r="C16" s="5">
+        <v>66007</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="5">
+        <v>4</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5">
+        <v>-1</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5"/>
+      <c r="W16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="X16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="5">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -32,7 +32,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="95">
+  <si>
+    <t>1普通技能2位移技能</t>
+  </si>
   <si>
     <t>selectParam</t>
   </si>
@@ -293,6 +296,27 @@
   </si>
   <si>
     <t>77013</t>
+  </si>
+  <si>
+    <t>#野蛮冲撞</t>
+  </si>
+  <si>
+    <t>冲撞</t>
+  </si>
+  <si>
+    <t>0,0,77014,77021</t>
+  </si>
+  <si>
+    <t>0,0,0,900</t>
+  </si>
+  <si>
+    <t>55003,55004,0,0</t>
+  </si>
+  <si>
+    <t>野蛮冲撞伤害</t>
+  </si>
+  <si>
+    <t>77020</t>
   </si>
 </sst>
 </file>
@@ -1285,12 +1309,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:AA16"/>
+  <dimension ref="B1:AA19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.75" style="1" customWidth="1"/>
     <col min="5" max="6" width="9.625" style="1" customWidth="1"/>
     <col min="7" max="8" width="11" style="1" customWidth="1"/>
     <col min="9" max="9" width="28.75" style="1" customWidth="1"/>
@@ -1303,264 +1328,267 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:27">
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="G1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="2:27">
       <c r="I2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="2:27">
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="2:27">
       <c r="C4" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:27">
       <c r="C5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="G5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="K5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:27">
       <c r="B6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1568,7 +1596,6 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="1"/>
       <c r="J6" s="5"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -1596,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" s="5">
         <v>2</v>
@@ -1605,25 +1632,25 @@
         <v>2000</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J7" s="5">
         <v>2</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
       <c r="P7" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5">
@@ -1642,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="X7" s="5" t="b">
         <v>1</v>
@@ -1659,7 +1686,7 @@
     </row>
     <row r="8" spans="2:27">
       <c r="B8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1694,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -1703,19 +1730,19 @@
         <v>5000</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J9" s="5">
         <v>2</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
@@ -1738,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="X9" s="5" t="b">
         <v>1</v>
@@ -1761,7 +1788,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F10" s="5">
         <v>3</v>
@@ -1770,20 +1797,20 @@
         <v>3000</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" s="5">
         <v>2</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
@@ -1820,7 +1847,7 @@
     </row>
     <row r="11" spans="2:27">
       <c r="B11" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1853,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F12" s="5">
         <v>2</v>
@@ -1862,10 +1889,10 @@
         <v>5000</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J12" s="5">
         <v>2</v>
@@ -1873,11 +1900,11 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N12" s="6"/>
       <c r="O12" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
@@ -1897,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X12" s="5" t="b">
         <v>1</v>
@@ -1920,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F13" s="5">
         <v>4</v>
@@ -1928,16 +1955,16 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="M13" s="6"/>
       <c r="O13" s="6"/>
@@ -1957,7 +1984,7 @@
       </c>
       <c r="V13" s="5"/>
       <c r="W13" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X13" s="5" t="b">
         <v>0</v>
@@ -1974,7 +2001,7 @@
     </row>
     <row r="14" spans="2:27">
       <c r="B14" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -2008,7 +2035,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F15" s="5">
         <v>2</v>
@@ -2017,10 +2044,10 @@
         <v>5000</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J15" s="5">
         <v>2</v>
@@ -2028,11 +2055,11 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N15" s="6"/>
       <c r="O15" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
@@ -2052,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="W15" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X15" s="5" t="b">
         <v>1</v>
@@ -2075,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16" s="5">
         <v>4</v>
@@ -2083,16 +2110,16 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J16" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M16" s="6"/>
       <c r="O16" s="6"/>
@@ -2112,7 +2139,7 @@
       </c>
       <c r="V16" s="5"/>
       <c r="W16" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X16" s="5" t="b">
         <v>0</v>
@@ -2124,6 +2151,137 @@
         <v>0</v>
       </c>
       <c r="AA16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:27">
+      <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="2:27">
+      <c r="C18" s="5">
+        <v>66008</v>
+      </c>
+      <c r="D18" s="5">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J18" s="5">
+        <v>2</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="R18" s="5">
+        <v>1000</v>
+      </c>
+      <c r="S18" s="5">
+        <v>1000</v>
+      </c>
+      <c r="T18" s="5">
+        <v>5000</v>
+      </c>
+      <c r="U18" s="5">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5"/>
+      <c r="W18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="X18" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:27">
+      <c r="C19" s="5">
+        <v>66009</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="5">
+        <v>4</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J19" s="5">
+        <v>2</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5">
+        <v>-1</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5"/>
+      <c r="W19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="X19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="5">
         <v>0</v>
       </c>
     </row>
